--- a/docs/ヴィレッジHP_ヒアリングシート.xlsx
+++ b/docs/ヴィレッジHP_ヒアリングシート.xlsx
@@ -11,10 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_TOP" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_事業内容" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_選ばれる理由" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_会社概要" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_会社概要ほか" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_お問い合わせ" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_写真リスト" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_デザイン・参考URL" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -532,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C31"/>
+  <dimension ref="B2:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -675,7 +673,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>04_会社概要     … 会社の基本情報（未確定の項目のご確認）</t>
+          <t>04_会社概要ほか  … 会社情報・ご提供写真・デザインのご希望をまとめて</t>
         </is>
       </c>
     </row>
@@ -686,48 +684,33 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>06_写真リスト    … ご提供いただきたい写真のチェックリスト</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>07_デザイン・参考URL … 色の好み・参考にしたいサイトのご記入</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="2" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>ご提出先</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>ホームページ制作担当</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Email：______________________（担当メールアドレス）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="23">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B21:C21"/>
@@ -740,13 +723,12 @@
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B26:C26"/>
     <mergeCell ref="B4:C4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1386,7 +1368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D24"/>
+  <dimension ref="B2:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1399,7 +1381,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>【会社概要】ヒアリングシート   ( 会社の基本情報 )</t>
+          <t>【会社概要ほか】ヒアリングシート   ( 会社情報・写真・デザイン )</t>
         </is>
       </c>
     </row>
@@ -1655,11 +1637,263 @@
       <c r="C24" s="9" t="inlineStr"/>
       <c r="D24" s="10" t="inlineStr"/>
     </row>
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="24" customHeight="1">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>■ ご提供いただきたい写真（右欄にメモをご記入ください）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>トップ背景（一番目立つ写真）</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>解体現場・重機・整地後の土地など、迫力のある横長写真がおすすめ</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>代表者の写真</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>中川様のお顔写真（スーツ・作業着どちらでも）※任意</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>会社ロゴのデータ</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>名刺のVマーク。画像データ（PNG/AI等）があれば高画質で掲載できます</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>解体工事の写真</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>施工前・施工中・施工後など（あるだけ）</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>重機・車両の写真</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>自社の重機・トラックなど</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>リフォーム・リノベ事例</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>ビフォーアフターがあると効果的</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>不動産・土地の写真</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>取扱い物件・造成地など</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>スタッフ・作業風景</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>働く様子が伝わる写真</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>会社外観・事務所</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>外観や看板など</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>※ スマートフォンで撮影した写真でも構いません。データはメール添付やギガファイル便等でお送りください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="6" customHeight="1"/>
+    <row r="38" ht="24" customHeight="1">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>■ サイトの色・雰囲気</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>メインカラー（ドラフト）</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>青 × 緑（名刺のVマークの色に合わせています）</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr"/>
+    </row>
+    <row r="40" ht="48" customHeight="1">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>色・雰囲気のご希望</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>※ 変更したい色や目指したい印象をご記入ください。
+（例：信頼感 / 誠実 / 力強い / 清潔感 / 親しみやすい / シンプル 等）</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41" ht="6" customHeight="1"/>
+    <row r="42" ht="24" customHeight="1">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>■ 参考にしたいサイト（あればURLをご記入ください）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="44" customHeight="1">
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>参考URL①</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>URL：
+良いと思った点：</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr"/>
+    </row>
+    <row r="44" ht="44" customHeight="1">
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>参考URL②</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>URL：
+良いと思った点：</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>その他ご要望・ご質問</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr"/>
+      <c r="D45" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B14:D14"/>
+  <mergeCells count="8">
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1672,7 +1906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D16"/>
+  <dimension ref="B2:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1827,477 +2061,49 @@
       </c>
       <c r="D16" s="10" t="inlineStr"/>
     </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:D22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="36" customHeight="1">
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>【ご提供写真リスト】ヒアリングシート   ( 全ページ共通 )</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>中央列＝現在の制作内容（ドラフト） ／ 右列＝ヒアリング記入欄（修正・ご希望をこちらにご記入ください）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>現在の制作内容（ドラフト）</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>ヒアリング記入欄</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>■ ご提供いただきたい写真（右欄にメモをご記入ください）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>トップ背景（一番目立つ写真）</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>解体現場・重機・整地後の土地など、迫力のある横長写真がおすすめ</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>代表者の写真</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>中川様のお顔写真（スーツ・作業着どちらでも）※任意</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>会社ロゴのデータ</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>名刺のVマーク。画像データ（PNG/AI等）があれば高画質で掲載できます</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>解体工事の写真</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>施工前・施工中・施工後など（あるだけ）</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>重機・車両の写真</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>自社の重機・トラックなど</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>リフォーム・リノベ事例</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>ビフォーアフターがあると効果的</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>不動産・土地の写真</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>取扱い物件・造成地など</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>スタッフ・作業風景</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>働く様子が伝わる写真</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>会社外観・事務所</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>外観や看板など</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>□ 提供できる　／　□ 後日用意　／　□ 撮影してほしい　／　□ 不要</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="6" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>※ スマートフォンで撮影した写真でも構いません。データはメール添付やギガファイル便等でお送りください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>■ その他ご提供いただける写真</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>その他 1</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr"/>
-      <c r="D19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>その他 2</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr"/>
-      <c r="D20" s="10" t="inlineStr"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>その他 3</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr"/>
-      <c r="D21" s="10" t="inlineStr"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>その他 4</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr"/>
-      <c r="D22" s="10" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B16:D16"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="4" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="36" customHeight="1">
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>【デザインのご希望・参考URL】ヒアリングシート   ( サイト全体の雰囲気 )</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>中央列＝現在の制作内容（ドラフト） ／ 右列＝ヒアリング記入欄（修正・ご希望をこちらにご記入ください）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>現在の制作内容（ドラフト）</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>ヒアリング記入欄</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>■ サイトの色（現在のドラフト）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>メインカラー</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>青 × 緑（名刺のVマークの色に合わせています）</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>色のご希望</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>※ 変更したい色・イメージ（例：もっと落ち着いた色 / 力強い印象 等）をご記入ください</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8" ht="6" customHeight="1"/>
-    <row r="9" ht="24" customHeight="1">
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>■ 全体の雰囲気</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>目指したい印象</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>※ 当てはまるものに○（複数可）：
-信頼感 / 誠実 / 力強い / 清潔感 / 親しみやすい / 高級感 / シンプル / その他（　　　）</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr"/>
-    </row>
-    <row r="11" ht="6" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>■ 参考にしたいサイト（あればURLをご記入ください）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>参考URL①</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>URL：
-良いと思った点：</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>参考URL②</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>URL：
-良いと思った点：</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>参考URL③</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>URL：
-良いと思った点：</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr"/>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>同業他社で気になるサイト</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>URL：</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr"/>
-    </row>
     <row r="17" ht="6" customHeight="1"/>
     <row r="18" ht="24" customHeight="1">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>■ その他ご要望・ご質問</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="80" customHeight="1">
+          <t>■ ホームページのアドレス（ドメイン）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1">
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>自由記入</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr"/>
+          <t>ご希望のドメイン</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>※ ホームページのURLに使いたい文字列のご希望があればご記入ください。
+　（例：village-kitakyushu.jp / village-kaitai.com など）
+　取得できるか確認し、こちらで取得手続きを行います。特に希望が無ければお任せでも大丈夫です。</t>
+        </is>
+      </c>
       <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>希望する末尾</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>※ ご希望があれば○：　.jp　/　.com　/　.co.jp　/　こだわらない</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B13:D13"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/ヴィレッジHP_ヒアリングシート.xlsx
+++ b/docs/ヴィレッジHP_ヒアリングシート.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\village\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\工事書類\㈱ヴィレッジ\新規事業\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FCF2BA-220D-4004-9690-55A5F63D5F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68ED9606-6D80-4F44-81D1-E01243507625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ヒアリングシート" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="93">
   <si>
     <t>株式会社ヴィレッジ 様　ホームページ ヒアリングシート</t>
   </si>
@@ -85,19 +85,12 @@
     <t>中古住宅を新たな価値へ。ライフスタイルに合わせた空間づくりをデザインから施工まで一貫して行います。</t>
   </si>
   <si>
-    <t>追加したい事業・対応エリア</t>
-  </si>
-  <si>
     <t>※ 追加事業や対応可能な市区町村があればご記入ください</t>
   </si>
   <si>
     <t>保有資格・許可番号</t>
   </si>
   <si>
-    <t>一級土木施工管理技士
-※ 建設業許可番号・解体工事業登録番号などあればご記入ください</t>
-  </si>
-  <si>
     <t>■ 選ばれる理由（会社の強み）</t>
   </si>
   <si>
@@ -122,9 +115,6 @@
     <t>他社に負けない点・実績</t>
   </si>
   <si>
-    <t>※ アピールしたいことがあればご記入ください</t>
-  </si>
-  <si>
     <t>■ 会社概要（名刺の情報。ご確認ください）</t>
   </si>
   <si>
@@ -164,13 +154,7 @@
     <t>設立・資本金・従業員数</t>
   </si>
   <si>
-    <t>※ 掲載したい場合のみご記入ください（未記入なら省略します）</t>
-  </si>
-  <si>
     <t>建設業許可／宅建免許 番号</t>
-  </si>
-  <si>
-    <t>※ あればご記入ください（信頼感アップに繋がります）</t>
   </si>
   <si>
     <t>■ ご提供いただきたい写真（右欄にチェック・メモ）</t>
@@ -323,15 +307,158 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>8:00〜19:00／日曜・祝日休み　※ 実際の時間をご記入ください</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>サイトの色（ドラフト）</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>URL：</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解体工事で未来のかけ橋を創造する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今後、新規事業で行う予定ですので、今回のホームページには掲載しない</t>
+    <rPh sb="0" eb="2">
+      <t>コンゴ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シンキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジギョウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>コンカイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ケイサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解体工事補助金申請の代行</t>
+    <rPh sb="0" eb="4">
+      <t>カイタイコウジ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ホジョキン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ダイコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一級土木施工管理技士
+※ 建設業許可番号・解体工事業登録番号などあればご記入ください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解体工事業登録番号：福岡県知事　第1456号　　　　　　　　　　　　　建築物石綿含有建材調査者：第21071177号</t>
+    <rPh sb="10" eb="15">
+      <t>フクオカケンチジ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ゴウ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ダイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近隣対策（工事着手前、工事完了後のあいさつ回り）クレームの少なさ</t>
+    <rPh sb="0" eb="2">
+      <t>キンリン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイサク</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>コウジチャクシュ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>コウジカンリョウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>スク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8:00〜18:00／日曜・祝日休み　※ 実際の時間をご記入ください</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設立：2024年</t>
+    <rPh sb="0" eb="2">
+      <t>セツリツ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解体工事業登録番号：福岡県知事　第1456号　　　　　　　　　　　　　建築物石綿含有建材調査者：第21071177号</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>信頼感・誠実・清潔感</t>
+    <rPh sb="0" eb="3">
+      <t>シンライカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイジツ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>セイケツカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>㈱クリーンアイランド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>㈱ACTIVE　岡山　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　㈱サンライズ　横浜市</t>
+    <rPh sb="8" eb="10">
+      <t>オカヤマ</t>
+    </rPh>
+    <rPh sb="49" eb="52">
+      <t>ヨコハマシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>.JPがいいです</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -470,19 +597,9 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -493,8 +610,18 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -865,431 +992,449 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:D54"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3" style="3" customWidth="1"/>
-    <col min="2" max="2" width="24" style="3" customWidth="1"/>
-    <col min="3" max="4" width="52" style="3" customWidth="1"/>
-    <col min="5" max="5" width="3" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="3" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24" style="1" customWidth="1"/>
+    <col min="3" max="4" width="52" style="1" customWidth="1"/>
+    <col min="5" max="5" width="3" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:4" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="2:4" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" spans="2:4" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="2:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
+      <c r="D6" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" spans="2:4" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="2:4" ht="45.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="7" t="s">
+    <row r="15" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="7" t="s">
+      <c r="D15" s="5"/>
+    </row>
+    <row r="16" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="2:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="2:4" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" spans="2:4" ht="44.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="9"/>
-    </row>
-    <row r="18" spans="2:4" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
+      <c r="C18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
+      <c r="D21" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="7" t="s">
+      <c r="D22" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C23" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="7" t="s">
+      <c r="D23" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C24" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="7" t="s">
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="25" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
+      <c r="C28" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="9"/>
-    </row>
-    <row r="28" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="7" t="s">
+      <c r="C29" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="9"/>
-    </row>
-    <row r="29" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="7" t="s">
+      <c r="C30" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="9"/>
-    </row>
-    <row r="30" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
+      <c r="C31" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="9"/>
-    </row>
-    <row r="31" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="7" t="s">
+      <c r="C32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="2:4" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C33" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="2:4" ht="33.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="9"/>
-    </row>
-    <row r="32" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="7" t="s">
+      <c r="C34" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="9"/>
-    </row>
-    <row r="33" spans="2:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="7" t="s">
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+    </row>
+    <row r="37" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C37" s="4"/>
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="9"/>
-    </row>
-    <row r="34" spans="2:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="7" t="s">
+      <c r="C38" s="4"/>
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C39" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="9"/>
-    </row>
-    <row r="35" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="6" t="s">
+      <c r="D39" s="5"/>
+    </row>
+    <row r="40" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="7" t="s">
+      <c r="C40" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="8"/>
-      <c r="D37" s="9"/>
-    </row>
-    <row r="38" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="7" t="s">
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="9"/>
-    </row>
-    <row r="39" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="7" t="s">
+      <c r="C41" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="D41" s="5"/>
+    </row>
+    <row r="42" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="9"/>
-    </row>
-    <row r="40" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="7" t="s">
+      <c r="C42" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="D42" s="5"/>
+    </row>
+    <row r="43" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D40" s="9"/>
-    </row>
-    <row r="41" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="7" t="s">
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+    </row>
+    <row r="44" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+    </row>
+    <row r="46" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D41" s="9"/>
-    </row>
-    <row r="42" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="7" t="s">
+      <c r="D46" s="5"/>
+    </row>
+    <row r="47" spans="2:4" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C47" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D42" s="9"/>
-    </row>
-    <row r="43" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="10" t="s">
+      <c r="D47" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" ht="44.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-    </row>
-    <row r="44" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="6" t="s">
+      <c r="C48" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" ht="44.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-    </row>
-    <row r="46" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C46" s="8" t="s">
+      <c r="C49" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D46" s="9"/>
-    </row>
-    <row r="47" spans="2:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="7" t="s">
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+    </row>
+    <row r="52" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C52" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D47" s="9"/>
-    </row>
-    <row r="48" spans="2:4" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="7" t="s">
+      <c r="D52" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D48" s="9"/>
-    </row>
-    <row r="49" spans="2:4" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="7" t="s">
+      <c r="C53" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D49" s="9"/>
-    </row>
-    <row r="50" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="2:4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="6" t="s">
+      <c r="D53" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-    </row>
-    <row r="52" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="7" t="s">
+      <c r="C54" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C52" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D52" s="9"/>
-    </row>
-    <row r="53" spans="2:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D53" s="9"/>
-    </row>
-    <row r="54" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D54" s="9"/>
+      <c r="D54" s="5" t="s">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="10">
